--- a/abalation/postscreen_ablation_summary.xlsx
+++ b/abalation/postscreen_ablation_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,217 +603,325 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Random selection</t>
+          <t>Full model</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>30800</v>
       </c>
       <c r="C2" t="n">
-        <v>647</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02100649350649351</v>
+        <v>0.002272727272727273</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5217478275299072</v>
+        <v>0.7907025218009949</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1478041559457779</v>
+        <v>0.02996029704809189</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5297626852989197</v>
+        <v>0.8041054606437683</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0919385626912117</v>
+        <v>0.7266068458557129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8195915818214417</v>
+        <v>0.8386080861091614</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4285444021224976</v>
+        <v>0.7246522903442383</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2201675623655319</v>
+        <v>0.03814022243022919</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N2" t="n">
-        <v>1.030783172704077</v>
+        <v>1.406645443451855</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5297177637952578</v>
+        <v>0.7228727616918712</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7775054518110308</v>
+        <v>0.8903893922530666</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2224945481889692</v>
+        <v>0.1096106077469335</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5965496897697449</v>
+        <v>0.9762219190597534</v>
       </c>
       <c r="S2" t="n">
-        <v>647</v>
+        <v>70</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04791344667697063</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="W2" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>0.115919629057187</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03709428129829984</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00463678516228748</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.04636785162287481</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE2" t="n">
-        <v>464</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.7171561051004637</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.03091190108191654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full model</t>
+          <t>Random selection</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>30800</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>647</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002272727272727273</v>
+        <v>0.02100649350649351</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7907025218009949</v>
+        <v>0.5217478275299072</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02996029704809189</v>
+        <v>0.1478041559457779</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8041054606437683</v>
+        <v>0.5297626852989197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7266068458557129</v>
+        <v>0.0919385626912117</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8386080861091614</v>
+        <v>0.8195915818214417</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7246522903442383</v>
+        <v>0.4285444021224976</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03814022243022919</v>
+        <v>0.2201675623655319</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.406645443451855</v>
+        <v>1.030783172704077</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7228727616918712</v>
+        <v>0.5297177637952578</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8903893922530666</v>
+        <v>0.7775054518110308</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1096106077469335</v>
+        <v>0.2224945481889692</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9762219190597534</v>
+        <v>0.5965496897697449</v>
       </c>
       <c r="S3" t="n">
-        <v>70</v>
+        <v>647</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.04791344667697063</v>
       </c>
       <c r="W3" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05714285714285714</v>
+        <v>0.115919629057187</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.03709428129829984</v>
       </c>
       <c r="AA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.00463678516228748</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.04636785162287481</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>464</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.7171561051004637</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.03091190108191654</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Morgan fingerprints</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1598</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05188311688311689</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4970982074737549</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1771570593118668</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4901220202445984</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.08984745293855667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8760542273521423</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.345262885093689</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2305876016616821</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.628475078717241</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8368706435432395</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7417190023919342</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2582809976080658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.4084196388721466</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1598</v>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.4142857142857143</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
+      <c r="U4" t="n">
+        <v>92</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.05757196495619524</v>
+      </c>
+      <c r="W4" t="n">
+        <v>292</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1827284105131414</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.04380475594493116</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.06758448060075094</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.03191489361702127</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>521</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.3260325406758448</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>464</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2903629536921151</v>
       </c>
     </row>
   </sheetData>

--- a/abalation/postscreen_ablation_summary.xlsx
+++ b/abalation/postscreen_ablation_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,328 @@
       </c>
       <c r="AH4" t="n">
         <v>0.2903629536921151</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>w/o EMA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05665584415584415</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1410341560840607</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04528848081827164</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1345290690660477</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.03464721888303757</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3032790422439575</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.06195394694805145</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03871873021125793</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.731253266568848</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8896881839119469</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8933446268918025</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1066553731081975</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4581439197063446</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1745</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>322</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1845272206303725</v>
+      </c>
+      <c r="W5" t="n">
+        <v>212</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1214899713467049</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.05444126074498568</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01489971346704871</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>197</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1128939828080229</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>482</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.27621776504298</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>411</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2355300859598854</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>w/o decorrelation</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2853</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.09262987012987013</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.09581029415130615</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03772776573896408</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.08138606697320938</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01841576583683491</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1956910789012909</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.04051141068339348</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02000768110156059</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5912028169874812</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3038181476541937</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8280096221910889</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1719903778089112</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.2066654860973358</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2853</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>252</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.08832807570977919</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.008412197686645636</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>164</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.05748335085874518</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.001051524710830704</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.8412197686645636</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.003505082369435682</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>w/o top-K</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03457792207792208</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2571951448917389</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.502114395814715e-06</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2571956217288971</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2571672797203064</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2572014927864075</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.05307357758283615</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.177291389671154e-05</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1/7</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8677499996152387</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1322500003847613</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>1065</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1065</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/abalation/postscreen_ablation_summary.xlsx
+++ b/abalation/postscreen_ablation_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,85 +516,160 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Known-additive similarity mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Known-additive similarity std</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Known-additive similarity median</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Known-additive similarity min</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Known-additive similarity max</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Novelty score mean</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Novelty score std</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Novelty score median</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Novelty score min</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Novelty score max</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>High similarity ratio &gt;0.75</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Moderate similarity ratio 0.40-0.75</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Low similarity ratio &lt;0.40</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Valid candidate SMILES for known similarity</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Invalid candidate SMILES for known similarity</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>Silhouette score</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Valid SMILES number</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Invalid SMILES number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Prototype 1 count</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Prototype 1 ratio</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Prototype 2 count</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Prototype 2 ratio</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Prototype 3 count</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Prototype 3 ratio</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Prototype 4 count</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Prototype 4 ratio</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Prototype 5 count</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Prototype 5 ratio</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Prototype 6 count</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Prototype 6 ratio</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Prototype 7 count</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Prototype 7 ratio</t>
         </is>
@@ -610,31 +685,31 @@
         <v>30800</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002272727272727273</v>
+        <v>0.002305194805194805</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7907025218009949</v>
+        <v>0.7898397445678711</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02996029704809189</v>
+        <v>0.03061173483729362</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8041054606437683</v>
+        <v>0.8040536046028137</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7266068458557129</v>
+        <v>0.7266066670417786</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8386080861091614</v>
+        <v>0.8386079072952271</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7246522903442383</v>
+        <v>0.7240567207336426</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03814022243022919</v>
+        <v>0.03819708526134491</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -645,66 +720,111 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="N2" t="n">
-        <v>1.406645443451855</v>
+        <v>1.407289832042097</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7228727616918712</v>
+        <v>0.7232039119202388</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8903893922530666</v>
+        <v>0.8981939482842489</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1096106077469335</v>
+        <v>0.1018060517157511</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9762219190597534</v>
+        <v>0.4024557294490829</v>
       </c>
       <c r="S2" t="n">
-        <v>70</v>
+        <v>0.2446103488706389</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="U2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5975442705509172</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.2446103488706389</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1267605633802817</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.2535211267605634</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6197183098591549</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9761408567428589</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>15</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="AK2" t="n">
+        <v>0.2112676056338028</v>
+      </c>
+      <c r="AL2" t="n">
         <v>4</v>
       </c>
-      <c r="X2" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AM2" t="n">
+        <v>0.05633802816901409</v>
+      </c>
+      <c r="AN2" t="n">
         <v>6</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.08571428571428572</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AO2" t="n">
+        <v>0.08450704225352113</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.2394366197183098</v>
+      </c>
+      <c r="AT2" t="n">
         <v>29</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0.4142857142857143</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AU2" t="n">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -759,60 +879,105 @@
         <v>0.5297177637952578</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7775054518110308</v>
+        <v>0.7829803806736025</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2224945481889692</v>
+        <v>0.2170196193263974</v>
       </c>
       <c r="R3" t="n">
+        <v>0.356477994370889</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0909621697872338</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.643522005629111</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0909621697872338</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.006182380216383307</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.2442040185471407</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.749613601236476</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>647</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.5965496897697449</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AH3" t="n">
         <v>647</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>31</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AK3" t="n">
         <v>0.04791344667697063</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AL3" t="n">
         <v>75</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AM3" t="n">
         <v>0.115919629057187</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AN3" t="n">
         <v>24</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AO3" t="n">
         <v>0.03709428129829984</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AP3" t="n">
         <v>3</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AQ3" t="n">
         <v>0.00463678516228748</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AR3" t="n">
         <v>30</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AS3" t="n">
         <v>0.04636785162287481</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AT3" t="n">
         <v>464</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AU3" t="n">
         <v>0.7171561051004637</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AV3" t="n">
         <v>20</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AW3" t="n">
         <v>0.03091190108191654</v>
       </c>
     </row>
@@ -867,60 +1032,105 @@
         <v>0.8368706435432395</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7417190023919342</v>
+        <v>0.7474231505385784</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2582809976080658</v>
+        <v>0.2525768494614216</v>
       </c>
       <c r="R4" t="n">
+        <v>0.3696038507309964</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.08746385088690187</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3584905660377358</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.6303961492690036</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.08746385088690187</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.6415094339622642</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.9130434782608696</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.007509386733416771</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.2909887359198999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.7015018773466833</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1598</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
         <v>0.4084196388721466</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AH4" t="n">
         <v>1598</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>92</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AK4" t="n">
         <v>0.05757196495619524</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AL4" t="n">
         <v>292</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AM4" t="n">
         <v>0.1827284105131414</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AN4" t="n">
         <v>70</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AO4" t="n">
         <v>0.04380475594493116</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AP4" t="n">
         <v>108</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AQ4" t="n">
         <v>0.06758448060075094</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AR4" t="n">
         <v>51</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AS4" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AT4" t="n">
         <v>521</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AU4" t="n">
         <v>0.3260325406758448</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AV4" t="n">
         <v>464</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AW4" t="n">
         <v>0.2903629536921151</v>
       </c>
     </row>
@@ -934,31 +1144,31 @@
         <v>30800</v>
       </c>
       <c r="C5" t="n">
-        <v>1745</v>
+        <v>573</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05665584415584415</v>
+        <v>0.01860389610389611</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1410341560840607</v>
+        <v>0.1412907987833023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04528848081827164</v>
+        <v>0.03656888008117676</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1345290690660477</v>
+        <v>0.1356883645057678</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03464721888303757</v>
+        <v>0.04395317658782005</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3032790422439575</v>
+        <v>0.3032787442207336</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06195394694805145</v>
+        <v>0.05010174214839935</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03871873021125793</v>
+        <v>0.03149263933300972</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -969,67 +1179,112 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.731253266568848</v>
+        <v>1.302420975768447</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8896881839119469</v>
+        <v>0.669311980514998</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8933446268918025</v>
+        <v>0.8101173445448631</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1066553731081975</v>
+        <v>0.189882655455137</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4581439197063446</v>
+        <v>0.3278362624851396</v>
       </c>
       <c r="S5" t="n">
-        <v>1745</v>
+        <v>0.1028543490548429</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="U5" t="n">
+        <v>0.1063829787234043</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.6721637375148604</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1028543490548429</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.6829268292682926</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01221640488656195</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1291448516579407</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.8586387434554974</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>573</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.253299742937088</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>573</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.07853403141361257</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>103</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.1797556719022688</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.08900523560209424</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.008726003490401396</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.001745200698080279</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.08027923211169284</v>
+      </c>
+      <c r="AV5" t="n">
         <v>322</v>
       </c>
-      <c r="V5" t="n">
-        <v>0.1845272206303725</v>
-      </c>
-      <c r="W5" t="n">
-        <v>212</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.1214899713467049</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.05444126074498568</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.01489971346704871</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>197</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.1128939828080229</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>482</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.27621776504298</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>411</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.2355300859598854</v>
+      <c r="AW5" t="n">
+        <v>0.5619546247818499</v>
       </c>
     </row>
     <row r="6">
@@ -1042,102 +1297,147 @@
         <v>30800</v>
       </c>
       <c r="C6" t="n">
-        <v>2853</v>
+        <v>1741</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09262987012987013</v>
+        <v>0.05652597402597403</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09581029415130615</v>
+        <v>0.08068738132715225</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03772776573896408</v>
+        <v>0.01489705126732588</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08138606697320938</v>
+        <v>0.07931117713451385</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01841576583683491</v>
+        <v>0.03142836689949036</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1956910789012909</v>
+        <v>0.1882775723934174</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04051141068339348</v>
+        <v>0.03529726341366768</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02000768110156059</v>
+        <v>0.01307844370603561</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5912028169874812</v>
+        <v>0.07211691206979612</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3038181476541937</v>
+        <v>0.03706076156949329</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8280096221910889</v>
+        <v>0.733830271584727</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1719903778089112</v>
+        <v>0.266169728415273</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2066654860973358</v>
+        <v>0.373034035295545</v>
       </c>
       <c r="S6" t="n">
-        <v>2853</v>
+        <v>0.08170448634307344</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="U6" t="n">
-        <v>252</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08832807570977919</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>24</v>
+        <v>0.626965964704455</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008412197686645636</v>
+        <v>0.08170448634307345</v>
       </c>
       <c r="Y6" t="n">
-        <v>164</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.05748335085874518</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001051524710830704</v>
+        <v>0.007466973004020678</v>
       </c>
       <c r="AC6" t="n">
-        <v>2400</v>
+        <v>0.3021252153934521</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.8412197686645636</v>
+        <v>0.6904078116025273</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>-0.2245469391345978</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.003505082369435682</v>
+        <v>1741</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.003446295232624928</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.003446295232624928</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1722</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.9890867317633544</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.00402067777139575</v>
       </c>
     </row>
     <row r="7">
@@ -1150,31 +1450,31 @@
         <v>30800</v>
       </c>
       <c r="C7" t="n">
-        <v>1065</v>
+        <v>297</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03457792207792208</v>
+        <v>0.009642857142857142</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2571951448917389</v>
+        <v>0.2571957409381866</v>
       </c>
       <c r="F7" t="n">
-        <v>3.502114395814715e-06</v>
+        <v>1.666287630541774e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2571956217288971</v>
+        <v>0.2571956515312195</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2571672797203064</v>
+        <v>0.25718754529953</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2572014927864075</v>
+        <v>0.2572012543678284</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05307357758283615</v>
+        <v>0.05308243632316589</v>
       </c>
       <c r="K7" t="n">
-        <v>2.177291389671154e-05</v>
+        <v>6.075879809941398e-06</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1191,58 +1491,103 @@
         <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8677499996152387</v>
+        <v>0.8660334987264147</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1322500003847613</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>0.1339665012735853</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3441749820173006</v>
+      </c>
       <c r="S7" t="n">
-        <v>1065</v>
+        <v>0.205965621550895</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6558250179826993</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.205965621550895</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.925</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.0707070707070707</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.2390572390572391</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>0.6902356902356902</v>
       </c>
       <c r="AE7" t="n">
-        <v>1065</v>
+        <v>297</v>
       </c>
       <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>297</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>297</v>
+      </c>
+      <c r="AU7" t="n">
         <v>1</v>
       </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/abalation/postscreen_ablation_summary.xlsx
+++ b/abalation/postscreen_ablation_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,191 +1137,191 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>w/o EMA</t>
+          <t>PCL encoder only</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>30800</v>
       </c>
       <c r="C5" t="n">
-        <v>573</v>
+        <v>404</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01860389610389611</v>
+        <v>0.01311688311688312</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1412907987833023</v>
+        <v>0.7286467552185059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03656888008117676</v>
+        <v>0.04572272673249245</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1356883645057678</v>
+        <v>0.7290864586830139</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04395317658782005</v>
+        <v>0.6202951669692993</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3032787442207336</v>
+        <v>0.8291915655136108</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05010174214839935</v>
+        <v>0.7066236734390259</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03149263933300972</v>
+        <v>0.06953314691781998</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N5" t="n">
-        <v>1.302420975768447</v>
+        <v>0.7869295634536805</v>
       </c>
       <c r="O5" t="n">
-        <v>0.669311980514998</v>
+        <v>0.404401798220598</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8101173445448631</v>
+        <v>0.7754751606926659</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.189882655455137</v>
+        <v>0.2245248393073341</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3278362624851396</v>
+        <v>0.3794201714356947</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1028543490548429</v>
+        <v>0.1127392280984243</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1063829787234043</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6721637375148604</v>
+        <v>0.6205798285643053</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1028543490548429</v>
+        <v>0.1127392280984244</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6829268292682926</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01221640488656195</v>
+        <v>0.01732673267326733</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1291448516579407</v>
+        <v>0.2920792079207921</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8586387434554974</v>
+        <v>0.6905940594059405</v>
       </c>
       <c r="AE5" t="n">
-        <v>573</v>
+        <v>404</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.253299742937088</v>
+        <v>0.9688802361488342</v>
       </c>
       <c r="AH5" t="n">
-        <v>573</v>
+        <v>404</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.07853403141361257</v>
+        <v>0.0297029702970297</v>
       </c>
       <c r="AL5" t="n">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1797556719022688</v>
+        <v>0.3886138613861386</v>
       </c>
       <c r="AN5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08900523560209424</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.008726003490401396</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001745200698080279</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>46</v>
+        <v>235</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.08027923211169284</v>
+        <v>0.5816831683168316</v>
       </c>
       <c r="AV5" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.5619546247818499</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>w/o decorrelation</t>
+          <t>USL encoder only</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>30800</v>
       </c>
       <c r="C6" t="n">
-        <v>1741</v>
+        <v>1622</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05652597402597403</v>
+        <v>0.05266233766233766</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08068738132715225</v>
+        <v>0.08542905002832413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01489705126732588</v>
+        <v>0.01082165725529194</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07931117713451385</v>
+        <v>0.0832306370139122</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03142836689949036</v>
+        <v>0.06476070731878281</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1882775723934174</v>
+        <v>0.1606500148773193</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03529726341366768</v>
+        <v>0.02130129374563694</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01307844370603561</v>
+        <v>0.01584317907691002</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1332,37 +1332,37 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07211691206979612</v>
+        <v>0.680070668254068</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03706076156949329</v>
+        <v>0.3494871891100542</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733830271584727</v>
+        <v>0.751665501958124</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.266169728415273</v>
+        <v>0.248334498041876</v>
       </c>
       <c r="R6" t="n">
-        <v>0.373034035295545</v>
+        <v>0.3677148841017495</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08170448634307344</v>
+        <v>0.08892310015245876</v>
       </c>
       <c r="T6" t="n">
         <v>0.3636363636363636</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.075</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.626965964704455</v>
+        <v>0.6322851158982506</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08170448634307345</v>
+        <v>0.08892310015245876</v>
       </c>
       <c r="Y6" t="n">
         <v>0.6363636363636364</v>
@@ -1371,28 +1371,28 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.925</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007466973004020678</v>
+        <v>0.004315659679408138</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3021252153934521</v>
+        <v>0.3070283600493218</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.6904078116025273</v>
+        <v>0.6886559802712701</v>
       </c>
       <c r="AE6" t="n">
-        <v>1741</v>
+        <v>1622</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.2245469391345978</v>
+        <v>-0.1852042227983475</v>
       </c>
       <c r="AH6" t="n">
-        <v>1741</v>
+        <v>1622</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1404,16 +1404,16 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>429</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.003446295232624928</v>
+        <v>0.2644882860665845</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.003446295232624928</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -1422,172 +1422,784 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1722</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.9890867317633544</v>
+        <v>0.0006165228113440197</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>0.7133168927250308</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.00402067777139575</v>
+        <v>0.02157829839704069</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>w/o top-K</t>
+          <t>PCL encoder clustering</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>30800</v>
       </c>
       <c r="C7" t="n">
+        <v>341</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01107142857142857</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5711333155632019</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1104985997080803</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5703426003456116</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1353694945573807</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8291916251182556</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5371402502059937</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1593528836965561</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8301091437191191</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4265917129432285</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7712943496779462</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2287056503220538</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3448892838653492</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.07438387665649995</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3454545454545455</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.6551107161346508</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.07438387665649995</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.6545454545454545</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.2228739002932551</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7771260997067448</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>341</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9159501791000366</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>341</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.01173020527859238</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.02932551319648094</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.05278592375366569</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>269</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.7888563049853372</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.05278592375366569</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USL encoder clustering</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C8" t="n">
+        <v>155</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.005032467532467532</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07985252887010574</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.02117422595620155</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.07709437608718872</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.04862787947058678</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1995557397603989</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.03904559835791588</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0122584281489253</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5067212969772699</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2604032345600691</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7673313722246951</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.232668627775305</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3237727776417914</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.06069108906850904</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.6762272223582085</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.06069108906850904</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.8688524590163934</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.1032258064516129</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.8967741935483871</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>155</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7860473394393921</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>155</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>129</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.832258064516129</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.1548387096774194</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>w/o EMA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C9" t="n">
+        <v>573</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01860389610389611</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1412907987833023</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03656888008117676</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1356883645057678</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.04395317658782005</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3032787442207336</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.05010174214839935</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.03149263933300972</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.302420975768447</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.669311980514998</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8101173445448631</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.189882655455137</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3278362624851396</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1028543490548429</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1063829787234043</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6721637375148604</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.1028543490548429</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6829268292682926</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.01221640488656195</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.1291448516579407</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8586387434554974</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.253299742937088</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.07853403141361257</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>103</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.1797556719022688</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.08900523560209424</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.008726003490401396</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.001745200698080279</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.08027923211169284</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>322</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.5619546247818499</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>w/o decorrelation</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1741</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.05652597402597403</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.08068738132715225</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01489705126732588</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.07931117713451385</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03142836689949036</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1882775723934174</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.03529726341366768</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01307844370603561</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.07211691206979612</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.03706076156949329</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.733830271584727</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.266169728415273</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.373034035295545</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.08170448634307344</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.626965964704455</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.08170448634307345</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.007466973004020678</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.3021252153934521</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6904078116025273</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1741</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.2245469391345978</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1741</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.003446295232624928</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.003446295232624928</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1722</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.9890867317633544</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.00402067777139575</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>w/o top-K</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C11" t="n">
         <v>297</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D11" t="n">
         <v>0.009642857142857142</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E11" t="n">
         <v>0.2571957409381866</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F11" t="n">
         <v>1.666287630541774e-06</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G11" t="n">
         <v>0.2571956515312195</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H11" t="n">
         <v>0.25718754529953</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I11" t="n">
         <v>0.2572012543678284</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J11" t="n">
         <v>0.05308243632316589</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K11" t="n">
         <v>6.075879809941398e-06</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1/7</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="M11" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N11" t="n">
         <v>-0</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O11" t="n">
         <v>-0</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P11" t="n">
         <v>0.8660334987264147</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q11" t="n">
         <v>0.1339665012735853</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R11" t="n">
         <v>0.3441749820173006</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S11" t="n">
         <v>0.205965621550895</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T11" t="n">
         <v>0.3076923076923077</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U11" t="n">
         <v>0.075</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W11" t="n">
         <v>0.6558250179826993</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X11" t="n">
         <v>0.205965621550895</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y11" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>0.925</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB11" t="n">
         <v>0.0707070707070707</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC11" t="n">
         <v>0.2390572390572391</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD11" t="n">
         <v>0.6902356902356902</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AE11" t="n">
         <v>297</v>
       </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
         <v>297</v>
       </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
         <v>297</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AU11" t="n">
         <v>1</v>
       </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
         <v>0</v>
       </c>
     </row>
